--- a/artfynd/A 51928-2022 artfynd.xlsx
+++ b/artfynd/A 51928-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51928-2022 artfynd.xlsx
+++ b/artfynd/A 51928-2022 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104885528</v>
+        <v>104885756</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,13 +711,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338879.445764879</v>
+        <v>338856</v>
       </c>
       <c r="R2" t="n">
-        <v>6572310.121027966</v>
+        <v>6572248</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,7 +746,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +756,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,37 +783,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104885756</v>
+        <v>104885528</v>
       </c>
       <c r="B3" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,13 +819,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338855.7678410808</v>
+        <v>338879</v>
       </c>
       <c r="R3" t="n">
-        <v>6572247.644139639</v>
+        <v>6572310</v>
       </c>
       <c r="S3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,7 +854,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +864,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,12 +894,7 @@
         <v>104885790</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -942,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338863.6241484784</v>
+        <v>338864</v>
       </c>
       <c r="R4" t="n">
-        <v>6572287.754814865</v>
+        <v>6572288</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,12 +1002,7 @@
         <v>109616630</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1054,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338871.2898586647</v>
+        <v>338871</v>
       </c>
       <c r="R5" t="n">
-        <v>6572299.20430477</v>
+        <v>6572299</v>
       </c>
       <c r="S5" t="n">
         <v>12</v>
@@ -1092,19 +1072,9 @@
           <t>2022-12-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-12-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
